--- a/Card4/Pandas/Exemplo_Excel.xlsx
+++ b/Card4/Pandas/Exemplo_Excel.xlsx
@@ -425,31 +425,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 0.2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0.1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>d</t>
         </is>
@@ -466,12 +476,18 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -483,15 +499,21 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -503,15 +525,21 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>11</v>
       </c>
     </row>
@@ -523,15 +551,21 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>13</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>14</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>15</v>
       </c>
     </row>
